--- a/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_11-11-2025.xlsx
+++ b/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_11-11-2025.xlsx
@@ -496,28 +496,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -553,28 +554,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -614,28 +616,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -675,28 +678,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -736,28 +740,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -797,28 +802,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -858,28 +864,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -919,28 +926,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1124,28 +1132,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1181,28 +1190,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1228,7 +1238,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '87.88Per'</t>
+          <t>Error: could not convert string to float: '95.67Per'</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1240,28 +1250,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1287,7 +1298,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '87.88Per'</t>
+          <t>Error: could not convert string to float: '95.67Per'</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1299,28 +1310,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1393,28 +1405,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1450,28 +1463,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1509,28 +1523,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -1568,28 +1583,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2110,28 +2126,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2171,28 +2188,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2454,28 +2472,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2515,28 +2534,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2872,28 +2892,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -2933,28 +2954,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -3216,28 +3238,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -3277,28 +3300,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
@@ -4187,28 +4211,29 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0xb758d3
-	0xb75914
-	0x98e76d
-	0x9da09d
-	0x9da47b
-	0xa21802
-	0x9fc9b4
-	0xa1eea6
-	0x9fc766
-	0x9cdac0
-	0x9cede4
-	0xdf7974
-	0xdf2bea
-	0xb9e5c4
-	0xb8dd38
-	0xb94d9d
-	0xb7dee8
-	0xb7e0ac
-	0xb67d2a
+	0x3158d3
+	0x315914
+	0x12e76d
+	0x17a09d
+	0x17a47b
+	0x1c1802
+	0x19c9b4
+	0x1beea6
+	0x19c766
+	0x16dac0
+	0x16ede4
+	0x597974
+	0x592bea
+	0x33e5c4
+	0x32dd38
+	0x334d9d
+	0x31dee8
+	0x31e0ac
+	0x307d2a
 	0x75ea5d49
 	0x7705d6db
 	0x7705d661
+	0
 </t>
         </is>
       </c>
